--- a/erp-server/erp-server-fms/src/main/resources/excel/assetCardTemplate.xlsx
+++ b/erp-server/erp-server-fms/src/main/resources/excel/assetCardTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <r>
       <rPr>
@@ -206,6 +206,20 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>供应商</t>
+    </r>
   </si>
   <si>
     <r>
@@ -306,7 +320,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,6 +491,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1468,29 +1488,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.81818181818182" customWidth="1"/>
-    <col min="2" max="2" width="15.9090909090909" customWidth="1"/>
-    <col min="3" max="4" width="18.8181818181818" customWidth="1"/>
-    <col min="5" max="5" width="16.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="12.0909090909091" customWidth="1"/>
-    <col min="7" max="7" width="12.9090909090909" customWidth="1"/>
-    <col min="8" max="8" width="13.5454545454545" customWidth="1"/>
-    <col min="9" max="9" width="12.6363636363636" customWidth="1"/>
-    <col min="10" max="10" width="17.1818181818182" customWidth="1"/>
-    <col min="11" max="11" width="13.6363636363636" customWidth="1"/>
-    <col min="12" max="12" width="13.2727272727273" customWidth="1"/>
-    <col min="13" max="14" width="14.4545454545455" customWidth="1"/>
-    <col min="15" max="15" width="10.8181818181818" customWidth="1"/>
-    <col min="16" max="16" width="15.2727272727273" customWidth="1"/>
-    <col min="17" max="17" width="15.5454545454545" customWidth="1"/>
-    <col min="18" max="18" width="12.2727272727273" customWidth="1"/>
-    <col min="19" max="19" width="15.9090909090909" customWidth="1"/>
+    <col min="1" max="1" width="9.81666666666667" customWidth="1"/>
+    <col min="2" max="2" width="15.9083333333333" customWidth="1"/>
+    <col min="3" max="4" width="18.8166666666667" customWidth="1"/>
+    <col min="5" max="5" width="16.1833333333333" customWidth="1"/>
+    <col min="6" max="6" width="12.0916666666667" customWidth="1"/>
+    <col min="7" max="7" width="12.9083333333333" customWidth="1"/>
+    <col min="8" max="8" width="13.5416666666667" customWidth="1"/>
+    <col min="9" max="9" width="12.6333333333333" customWidth="1"/>
+    <col min="10" max="11" width="17.1833333333333" customWidth="1"/>
+    <col min="12" max="12" width="13.6333333333333" customWidth="1"/>
+    <col min="13" max="13" width="13.275" customWidth="1"/>
+    <col min="14" max="15" width="14.4583333333333" customWidth="1"/>
+    <col min="16" max="16" width="10.8166666666667" customWidth="1"/>
+    <col min="17" max="17" width="15.275" customWidth="1"/>
+    <col min="18" max="18" width="15.5416666666667" customWidth="1"/>
+    <col min="19" max="19" width="12.275" customWidth="1"/>
+    <col min="20" max="20" width="15.9083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13.5" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="12.75" spans="1:19">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1530,13 +1550,16 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -1552,7 +1575,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
       <formula1>"购入"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
       <formula1>"折旧费"</formula1>
     </dataValidation>
   </dataValidations>
